--- a/results/results_iter2.xlsx
+++ b/results/results_iter2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/danemerson/Documents/CMU/01_Research/Projects/CPA/Bayesian Optimization/cpa-bayesian-opt/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1857A16C-EECD-4A49-B0E1-AF8D189A538F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE5C97DB-14B9-BB4D-9625-F65386126310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="19980" xr2:uid="{732449FA-1918-F249-870A-9891F3ECE17F}"/>
   </bookViews>
